--- a/CartRules_1126.xlsx
+++ b/CartRules_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="45">
   <si>
     <t>Product ID</t>
   </si>
@@ -23,6 +23,132 @@
   </si>
   <si>
     <t>Cart Rules</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>13928</t>
+  </si>
+  <si>
+    <t>2859</t>
+  </si>
+  <si>
+    <t>25345</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>10597</t>
+  </si>
+  <si>
+    <t>11427</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>11234</t>
+  </si>
+  <si>
+    <t>2423</t>
+  </si>
+  <si>
+    <t>3583</t>
+  </si>
+  <si>
+    <t>13023</t>
+  </si>
+  <si>
+    <t>4032</t>
+  </si>
+  <si>
+    <t>11856</t>
+  </si>
+  <si>
+    <t>9373</t>
+  </si>
+  <si>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>8557</t>
+  </si>
+  <si>
+    <t>9841</t>
+  </si>
+  <si>
+    <t>6575</t>
+  </si>
+  <si>
+    <t>8927</t>
+  </si>
+  <si>
+    <t>8945</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>7457</t>
+  </si>
+  <si>
+    <t>22587</t>
+  </si>
+  <si>
+    <t>8943</t>
+  </si>
+  <si>
+    <t>9081</t>
+  </si>
+  <si>
+    <t>13244</t>
+  </si>
+  <si>
+    <t>8283</t>
+  </si>
+  <si>
+    <t>944</t>
+  </si>
+  <si>
+    <t>9877</t>
+  </si>
+  <si>
+    <t>3429</t>
+  </si>
+  <si>
+    <t>11151</t>
+  </si>
+  <si>
+    <t>9138</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
 </sst>
 </file>
@@ -380,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -395,333 +521,399 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>94</v>
-      </c>
-      <c r="B2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>130</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>69</v>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
-        <v>950</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>69</v>
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>972</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>115</v>
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>1309</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>63</v>
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>2109</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>542</v>
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
-        <v>2423</v>
-      </c>
-      <c r="B8">
-        <v>80</v>
-      </c>
-      <c r="C8">
-        <v>219</v>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
-        <v>2438</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>761</v>
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
-        <v>5584</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>286</v>
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
-        <v>5729</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>60</v>
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12">
-        <v>5733</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>60</v>
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13">
-        <v>6496</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>47</v>
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14">
-        <v>6627</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15">
-        <v>7704</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>208</v>
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16">
-        <v>7705</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>208</v>
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17">
-        <v>7708</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>208</v>
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18">
-        <v>7887</v>
-      </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18">
-        <v>163</v>
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19">
-        <v>8283</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>208</v>
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20">
-        <v>9068</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>141</v>
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21">
-        <v>9690</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>91</v>
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22">
-        <v>10093</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>963</v>
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23">
-        <v>10147</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>78</v>
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24">
-        <v>10993</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>64</v>
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25">
-        <v>12229</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>180</v>
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26">
-        <v>12721</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>338</v>
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27">
-        <v>18964</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>80</v>
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28">
-        <v>21712</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>1624</v>
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29">
-        <v>21713</v>
-      </c>
-      <c r="B29">
-        <v>3</v>
-      </c>
-      <c r="C29">
-        <v>1312</v>
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30">
-        <v>22125</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30">
-        <v>73</v>
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31">
-        <v>22565</v>
-      </c>
-      <c r="B31">
-        <v>3</v>
-      </c>
-      <c r="C31">
-        <v>685</v>
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
